--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15418,7 +15418,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -24403,7 +24403,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -24642,7 +24642,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26523,7 +26523,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -32539,7 +32539,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -33527,7 +33527,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -35508,7 +35508,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -35747,7 +35747,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -37628,7 +37628,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -43644,7 +43644,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -44632,7 +44632,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -46613,7 +46613,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -46852,7 +46852,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -48733,7 +48733,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -54749,7 +54749,7 @@
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
@@ -55737,7 +55737,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -57025,16 +57025,16 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O362" t="n">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q362" t="n">
         <v>0</v>
       </c>
       <c r="R362" t="n">
-        <v>0.846892856697124</v>
+        <v>0.844954886773332</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
@@ -57718,7 +57718,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -57957,7 +57957,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -59838,7 +59838,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -63538,16 +63538,16 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O404" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q404" t="n">
         <v>0</v>
       </c>
       <c r="R404" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.2403082705502137</v>
       </c>
       <c r="S404" t="inlineStr">
         <is>
@@ -65854,7 +65854,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -66598,16 +66598,16 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>5100</v>
+        <v>5095</v>
       </c>
       <c r="O424" t="n">
-        <v>5100</v>
+        <v>5095</v>
       </c>
       <c r="Q424" t="n">
         <v>0</v>
       </c>
       <c r="R424" t="n">
-        <v>9.883646611339435</v>
+        <v>9.873956761720473</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -66760,10 +66760,10 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>5100</v>
+        <v>5095</v>
       </c>
       <c r="O425" t="n">
-        <v>5100</v>
+        <v>5095</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
@@ -66842,7 +66842,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -68130,16 +68130,16 @@
         </is>
       </c>
       <c r="N433" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="O433" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="Q433" t="n">
         <v>0</v>
       </c>
       <c r="R433" t="n">
-        <v>0.8585206762398764</v>
+        <v>0.8643345860112523</v>
       </c>
       <c r="S433" t="inlineStr">
         <is>
@@ -68278,16 +68278,16 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O434" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q434" t="n">
         <v>0</v>
       </c>
       <c r="R434" t="n">
-        <v>0.1782932329888682</v>
+        <v>0.1802312029126603</v>
       </c>
       <c r="S434" t="inlineStr">
         <is>
@@ -68823,7 +68823,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -69062,7 +69062,7 @@
       </c>
       <c r="AJ438" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK438" t="inlineStr">
@@ -70107,16 +70107,16 @@
         </is>
       </c>
       <c r="N445" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O445" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q445" t="n">
         <v>0</v>
       </c>
       <c r="R445" t="n">
-        <v>0.09883646611339433</v>
+        <v>0.1007744360371864</v>
       </c>
       <c r="S445" t="inlineStr">
         <is>
@@ -70403,16 +70403,16 @@
         </is>
       </c>
       <c r="N447" t="n">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="O447" t="n">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="Q447" t="n">
         <v>0</v>
       </c>
       <c r="R447" t="n">
-        <v>1.62983270590911</v>
+        <v>1.643398495375655</v>
       </c>
       <c r="S447" t="inlineStr">
         <is>
@@ -70699,16 +70699,16 @@
         </is>
       </c>
       <c r="N449" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O449" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q449" t="n">
         <v>0</v>
       </c>
       <c r="R449" t="n">
-        <v>0.3643383456729046</v>
+        <v>0.3624003757491125</v>
       </c>
       <c r="S449" t="inlineStr">
         <is>
@@ -70861,10 +70861,10 @@
         </is>
       </c>
       <c r="N450" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O450" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="U450" t="inlineStr">
         <is>
@@ -70943,7 +70943,7 @@
       </c>
       <c r="AJ450" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK450" t="inlineStr">
@@ -71095,16 +71095,16 @@
         </is>
       </c>
       <c r="N451" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O451" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q451" t="n">
         <v>0</v>
       </c>
       <c r="R451" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S451" t="inlineStr">
         <is>
@@ -71243,16 +71243,16 @@
         </is>
       </c>
       <c r="N452" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="O452" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="Q452" t="n">
         <v>0</v>
       </c>
       <c r="R452" t="n">
-        <v>0.1550375939033637</v>
+        <v>0.1627894735985319</v>
       </c>
       <c r="S452" t="inlineStr">
         <is>
@@ -71391,16 +71391,16 @@
         </is>
       </c>
       <c r="N453" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O453" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Q453" t="n">
         <v>0</v>
       </c>
       <c r="R453" t="n">
-        <v>1.143402255037307</v>
+        <v>1.145340224961099</v>
       </c>
       <c r="S453" t="inlineStr">
         <is>
@@ -72575,16 +72575,16 @@
         </is>
       </c>
       <c r="N461" t="n">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="O461" t="n">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="Q461" t="n">
         <v>0</v>
       </c>
       <c r="R461" t="n">
-        <v>4.854614659099075</v>
+        <v>4.856552629022867</v>
       </c>
       <c r="S461" t="inlineStr">
         <is>
@@ -73903,16 +73903,16 @@
         </is>
       </c>
       <c r="N470" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O470" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q470" t="n">
         <v>0</v>
       </c>
       <c r="R470" t="n">
-        <v>0.04263533832342501</v>
+        <v>0.04457330824721705</v>
       </c>
       <c r="S470" t="inlineStr">
         <is>
@@ -74051,16 +74051,16 @@
         </is>
       </c>
       <c r="N471" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O471" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q471" t="n">
         <v>0</v>
       </c>
       <c r="R471" t="n">
-        <v>0.1647274435223239</v>
+        <v>0.168603383369908</v>
       </c>
       <c r="S471" t="inlineStr">
         <is>
@@ -76959,7 +76959,7 @@
       </c>
       <c r="AJ490" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK490" t="inlineStr">
@@ -77703,16 +77703,16 @@
         </is>
       </c>
       <c r="N495" t="n">
-        <v>5538</v>
+        <v>5545</v>
       </c>
       <c r="O495" t="n">
-        <v>5538</v>
+        <v>5545</v>
       </c>
       <c r="Q495" t="n">
         <v>0</v>
       </c>
       <c r="R495" t="n">
-        <v>10.73247743796035</v>
+        <v>10.74604322742689</v>
       </c>
       <c r="S495" t="inlineStr">
         <is>
@@ -77865,10 +77865,10 @@
         </is>
       </c>
       <c r="N496" t="n">
-        <v>5538</v>
+        <v>5545</v>
       </c>
       <c r="O496" t="n">
-        <v>5538</v>
+        <v>5545</v>
       </c>
       <c r="U496" t="inlineStr">
         <is>
@@ -77947,7 +77947,7 @@
       </c>
       <c r="AJ496" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK496" t="inlineStr">
@@ -78939,16 +78939,16 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O502" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q502" t="n">
         <v>0</v>
       </c>
       <c r="R502" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.03682142855204888</v>
       </c>
       <c r="S502" t="inlineStr">
         <is>
@@ -79235,16 +79235,16 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="O504" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="Q504" t="n">
         <v>0</v>
       </c>
       <c r="R504" t="n">
-        <v>0.0717048871803057</v>
+        <v>0.1375958645892353</v>
       </c>
       <c r="S504" t="inlineStr">
         <is>
@@ -79383,16 +79383,16 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O505" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q505" t="n">
         <v>0</v>
       </c>
       <c r="R505" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="S505" t="inlineStr">
         <is>
@@ -79928,7 +79928,7 @@
       </c>
       <c r="AJ508" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK508" t="inlineStr">
@@ -80167,7 +80167,7 @@
       </c>
       <c r="AJ509" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK509" t="inlineStr">
@@ -80916,16 +80916,16 @@
         </is>
       </c>
       <c r="N514" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O514" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q514" t="n">
         <v>0</v>
       </c>
       <c r="R514" t="n">
-        <v>0</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S514" t="inlineStr">
         <is>
@@ -81212,16 +81212,16 @@
         </is>
       </c>
       <c r="N516" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O516" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q516" t="n">
         <v>0</v>
       </c>
       <c r="R516" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S516" t="inlineStr">
         <is>
@@ -81508,16 +81508,16 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="O518" t="n">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="Q518" t="n">
         <v>0</v>
       </c>
       <c r="R518" t="n">
-        <v>0.1104642856561466</v>
+        <v>0.1976729322267887</v>
       </c>
       <c r="S518" t="inlineStr">
         <is>
@@ -81804,16 +81804,16 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="O520" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="Q520" t="n">
         <v>0</v>
       </c>
       <c r="R520" t="n">
-        <v>0.04844924809480115</v>
+        <v>0.06976691725651366</v>
       </c>
       <c r="S520" t="inlineStr">
         <is>
@@ -81966,10 +81966,10 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="O521" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="U521" t="inlineStr">
         <is>
@@ -82048,7 +82048,7 @@
       </c>
       <c r="AJ521" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK521" t="inlineStr">
@@ -82348,16 +82348,16 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O523" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q523" t="n">
         <v>0</v>
       </c>
       <c r="R523" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S523" t="inlineStr">
         <is>
@@ -82496,16 +82496,16 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="O524" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="Q524" t="n">
         <v>0</v>
       </c>
       <c r="R524" t="n">
-        <v>0.1511616540557796</v>
+        <v>0.1666654134461159</v>
       </c>
       <c r="S524" t="inlineStr">
         <is>
@@ -83680,16 +83680,16 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="O532" t="n">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="Q532" t="n">
         <v>0</v>
       </c>
       <c r="R532" t="n">
-        <v>0.6724755635558399</v>
+        <v>0.7461184206599377</v>
       </c>
       <c r="S532" t="inlineStr">
         <is>
@@ -85008,16 +85008,16 @@
         </is>
       </c>
       <c r="N541" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O541" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q541" t="n">
         <v>0</v>
       </c>
       <c r="R541" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S541" t="inlineStr">
         <is>
@@ -85748,16 +85748,16 @@
         </is>
       </c>
       <c r="N546" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O546" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q546" t="n">
         <v>0</v>
       </c>
       <c r="R546" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S546" t="inlineStr">
         <is>
@@ -88064,7 +88064,7 @@
       </c>
       <c r="AJ561" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK561" t="inlineStr">
@@ -88808,16 +88808,16 @@
         </is>
       </c>
       <c r="N566" t="n">
-        <v>1125</v>
+        <v>1438</v>
       </c>
       <c r="O566" t="n">
-        <v>1125</v>
+        <v>1438</v>
       </c>
       <c r="Q566" t="n">
         <v>0</v>
       </c>
       <c r="R566" t="n">
-        <v>2.180216164266052</v>
+        <v>2.786800750412962</v>
       </c>
       <c r="S566" t="inlineStr">
         <is>
@@ -88970,10 +88970,10 @@
         </is>
       </c>
       <c r="N567" t="n">
-        <v>1125</v>
+        <v>1438</v>
       </c>
       <c r="O567" t="n">
-        <v>1125</v>
+        <v>1438</v>
       </c>
       <c r="U567" t="inlineStr">
         <is>
@@ -89052,7 +89052,7 @@
       </c>
       <c r="AJ567" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK567" t="inlineStr">
@@ -89711,7 +89711,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>73252</v>
+        <v>73750</v>
       </c>
     </row>
     <row r="16">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15418,7 +15418,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -24403,7 +24403,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -24642,7 +24642,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26523,7 +26523,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -32539,7 +32539,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -33527,7 +33527,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -35508,7 +35508,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -35747,7 +35747,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -37628,7 +37628,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -43644,7 +43644,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -44632,7 +44632,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -46613,7 +46613,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -46852,7 +46852,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -48733,7 +48733,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -54749,7 +54749,7 @@
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
@@ -55737,7 +55737,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -56729,16 +56729,16 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O360" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q360" t="n">
         <v>0</v>
       </c>
       <c r="R360" t="n">
-        <v>0.3817800749870331</v>
+        <v>0.3837180449108251</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
@@ -57173,16 +57173,16 @@
         </is>
       </c>
       <c r="N363" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O363" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q363" t="n">
         <v>0</v>
       </c>
       <c r="R363" t="n">
-        <v>0.1511616540557796</v>
+        <v>0.1472857142081955</v>
       </c>
       <c r="S363" t="inlineStr">
         <is>
@@ -57718,7 +57718,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -57957,7 +57957,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -59838,7 +59838,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -60138,16 +60138,16 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O381" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q381" t="n">
         <v>0</v>
       </c>
       <c r="R381" t="n">
-        <v>0.1530996239795716</v>
+        <v>0.1550375939033637</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
@@ -62946,16 +62946,16 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O400" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Q400" t="n">
         <v>0</v>
       </c>
       <c r="R400" t="n">
-        <v>0.1143402255037307</v>
+        <v>0.1104642856561466</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
@@ -65854,7 +65854,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -66598,16 +66598,16 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>5095</v>
+        <v>5090</v>
       </c>
       <c r="O424" t="n">
-        <v>5095</v>
+        <v>5090</v>
       </c>
       <c r="Q424" t="n">
         <v>0</v>
       </c>
       <c r="R424" t="n">
-        <v>9.873956761720473</v>
+        <v>9.864266912101515</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -66760,10 +66760,10 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>5095</v>
+        <v>5090</v>
       </c>
       <c r="O425" t="n">
-        <v>5095</v>
+        <v>5090</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
@@ -66842,7 +66842,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -68823,7 +68823,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -69062,7 +69062,7 @@
       </c>
       <c r="AJ438" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK438" t="inlineStr">
@@ -70403,16 +70403,16 @@
         </is>
       </c>
       <c r="N447" t="n">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="O447" t="n">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="Q447" t="n">
         <v>0</v>
       </c>
       <c r="R447" t="n">
-        <v>1.643398495375655</v>
+        <v>1.645336465299447</v>
       </c>
       <c r="S447" t="inlineStr">
         <is>
@@ -70699,16 +70699,16 @@
         </is>
       </c>
       <c r="N449" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O449" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q449" t="n">
         <v>0</v>
       </c>
       <c r="R449" t="n">
-        <v>0.3624003757491125</v>
+        <v>0.3643383456729046</v>
       </c>
       <c r="S449" t="inlineStr">
         <is>
@@ -70861,10 +70861,10 @@
         </is>
       </c>
       <c r="N450" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O450" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="U450" t="inlineStr">
         <is>
@@ -70943,7 +70943,7 @@
       </c>
       <c r="AJ450" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK450" t="inlineStr">
@@ -72575,16 +72575,16 @@
         </is>
       </c>
       <c r="N461" t="n">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="O461" t="n">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="Q461" t="n">
         <v>0</v>
       </c>
       <c r="R461" t="n">
-        <v>4.856552629022867</v>
+        <v>4.860428568870451</v>
       </c>
       <c r="S461" t="inlineStr">
         <is>
@@ -74051,16 +74051,16 @@
         </is>
       </c>
       <c r="N471" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O471" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="Q471" t="n">
         <v>0</v>
       </c>
       <c r="R471" t="n">
-        <v>0.168603383369908</v>
+        <v>0.1647274435223239</v>
       </c>
       <c r="S471" t="inlineStr">
         <is>
@@ -74643,16 +74643,16 @@
         </is>
       </c>
       <c r="N475" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="O475" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="Q475" t="n">
         <v>0</v>
       </c>
       <c r="R475" t="n">
-        <v>0.2635639096357182</v>
+        <v>0.2713157893308865</v>
       </c>
       <c r="S475" t="inlineStr">
         <is>
@@ -76959,7 +76959,7 @@
       </c>
       <c r="AJ490" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK490" t="inlineStr">
@@ -77703,16 +77703,16 @@
         </is>
       </c>
       <c r="N495" t="n">
-        <v>5545</v>
+        <v>5554</v>
       </c>
       <c r="O495" t="n">
-        <v>5545</v>
+        <v>5554</v>
       </c>
       <c r="Q495" t="n">
         <v>0</v>
       </c>
       <c r="R495" t="n">
-        <v>10.74604322742689</v>
+        <v>10.76348495674102</v>
       </c>
       <c r="S495" t="inlineStr">
         <is>
@@ -77865,10 +77865,10 @@
         </is>
       </c>
       <c r="N496" t="n">
-        <v>5545</v>
+        <v>5554</v>
       </c>
       <c r="O496" t="n">
-        <v>5545</v>
+        <v>5554</v>
       </c>
       <c r="U496" t="inlineStr">
         <is>
@@ -77947,7 +77947,7 @@
       </c>
       <c r="AJ496" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK496" t="inlineStr">
@@ -78939,16 +78939,16 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O502" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q502" t="n">
         <v>0</v>
       </c>
       <c r="R502" t="n">
-        <v>0.03682142855204888</v>
+        <v>0.0465112781710091</v>
       </c>
       <c r="S502" t="inlineStr">
         <is>
@@ -79235,16 +79235,16 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="O504" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="Q504" t="n">
         <v>0</v>
       </c>
       <c r="R504" t="n">
-        <v>0.1375958645892353</v>
+        <v>0.1860451126840364</v>
       </c>
       <c r="S504" t="inlineStr">
         <is>
@@ -79383,16 +79383,16 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O505" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q505" t="n">
         <v>0</v>
       </c>
       <c r="R505" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S505" t="inlineStr">
         <is>
@@ -79928,7 +79928,7 @@
       </c>
       <c r="AJ508" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK508" t="inlineStr">
@@ -80167,7 +80167,7 @@
       </c>
       <c r="AJ509" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK509" t="inlineStr">
@@ -80472,16 +80472,16 @@
         </is>
       </c>
       <c r="N511" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O511" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q511" t="n">
         <v>0</v>
       </c>
       <c r="R511" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S511" t="inlineStr">
         <is>
@@ -81212,16 +81212,16 @@
         </is>
       </c>
       <c r="N516" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O516" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q516" t="n">
         <v>0</v>
       </c>
       <c r="R516" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.02713157893308864</v>
       </c>
       <c r="S516" t="inlineStr">
         <is>
@@ -81508,16 +81508,16 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="O518" t="n">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="Q518" t="n">
         <v>0</v>
       </c>
       <c r="R518" t="n">
-        <v>0.1976729322267887</v>
+        <v>0.2422462404740058</v>
       </c>
       <c r="S518" t="inlineStr">
         <is>
@@ -81804,16 +81804,16 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="O520" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Q520" t="n">
         <v>0</v>
       </c>
       <c r="R520" t="n">
-        <v>0.06976691725651366</v>
+        <v>0.08527067664685002</v>
       </c>
       <c r="S520" t="inlineStr">
         <is>
@@ -81966,10 +81966,10 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="O521" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="U521" t="inlineStr">
         <is>
@@ -82048,7 +82048,7 @@
       </c>
       <c r="AJ521" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK521" t="inlineStr">
@@ -82348,16 +82348,16 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O523" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q523" t="n">
         <v>0</v>
       </c>
       <c r="R523" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.02713157893308864</v>
       </c>
       <c r="S523" t="inlineStr">
         <is>
@@ -82496,16 +82496,16 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="O524" t="n">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="Q524" t="n">
         <v>0</v>
       </c>
       <c r="R524" t="n">
-        <v>0.1666654134461159</v>
+        <v>0.2422462404740058</v>
       </c>
       <c r="S524" t="inlineStr">
         <is>
@@ -83680,16 +83680,16 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>385</v>
+        <v>552</v>
       </c>
       <c r="O532" t="n">
-        <v>385</v>
+        <v>552</v>
       </c>
       <c r="Q532" t="n">
         <v>0</v>
       </c>
       <c r="R532" t="n">
-        <v>0.7461184206599377</v>
+        <v>1.069759397933209</v>
       </c>
       <c r="S532" t="inlineStr">
         <is>
@@ -83976,16 +83976,16 @@
         </is>
       </c>
       <c r="N534" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O534" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q534" t="n">
         <v>0</v>
       </c>
       <c r="R534" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S534" t="inlineStr">
         <is>
@@ -85156,16 +85156,16 @@
         </is>
       </c>
       <c r="N542" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O542" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q542" t="n">
         <v>0</v>
       </c>
       <c r="R542" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="S542" t="inlineStr">
         <is>
@@ -85600,16 +85600,16 @@
         </is>
       </c>
       <c r="N545" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O545" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q545" t="n">
         <v>0</v>
       </c>
       <c r="R545" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S545" t="inlineStr">
         <is>
@@ -85748,16 +85748,16 @@
         </is>
       </c>
       <c r="N546" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O546" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q546" t="n">
         <v>0</v>
       </c>
       <c r="R546" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S546" t="inlineStr">
         <is>
@@ -86488,16 +86488,16 @@
         </is>
       </c>
       <c r="N551" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O551" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q551" t="n">
         <v>0</v>
       </c>
       <c r="R551" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S551" t="inlineStr">
         <is>
@@ -88064,7 +88064,7 @@
       </c>
       <c r="AJ561" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK561" t="inlineStr">
@@ -88808,16 +88808,16 @@
         </is>
       </c>
       <c r="N566" t="n">
-        <v>1438</v>
+        <v>1827</v>
       </c>
       <c r="O566" t="n">
-        <v>1438</v>
+        <v>1827</v>
       </c>
       <c r="Q566" t="n">
         <v>0</v>
       </c>
       <c r="R566" t="n">
-        <v>2.786800750412962</v>
+        <v>3.540671050768068</v>
       </c>
       <c r="S566" t="inlineStr">
         <is>
@@ -88970,10 +88970,10 @@
         </is>
       </c>
       <c r="N567" t="n">
-        <v>1438</v>
+        <v>1827</v>
       </c>
       <c r="O567" t="n">
-        <v>1438</v>
+        <v>1827</v>
       </c>
       <c r="U567" t="inlineStr">
         <is>
@@ -89052,7 +89052,7 @@
       </c>
       <c r="AJ567" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK567" t="inlineStr">
@@ -89711,7 +89711,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>73750</v>
+        <v>74432</v>
       </c>
     </row>
     <row r="16">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -64130,16 +64130,16 @@
         </is>
       </c>
       <c r="N408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q408" t="n">
         <v>0</v>
       </c>
       <c r="R408" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S408" t="inlineStr">
         <is>
@@ -66598,16 +66598,16 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>5090</v>
+        <v>5089</v>
       </c>
       <c r="O424" t="n">
-        <v>5090</v>
+        <v>5089</v>
       </c>
       <c r="Q424" t="n">
         <v>0</v>
       </c>
       <c r="R424" t="n">
-        <v>9.864266912101515</v>
+        <v>9.862328942177722</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -66760,10 +66760,10 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>5090</v>
+        <v>5089</v>
       </c>
       <c r="O425" t="n">
-        <v>5090</v>
+        <v>5089</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
@@ -68130,16 +68130,16 @@
         </is>
       </c>
       <c r="N433" t="n">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="O433" t="n">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="Q433" t="n">
         <v>0</v>
       </c>
       <c r="R433" t="n">
-        <v>0.8643345860112523</v>
+        <v>0.8604586461636684</v>
       </c>
       <c r="S433" t="inlineStr">
         <is>
@@ -71243,16 +71243,16 @@
         </is>
       </c>
       <c r="N452" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O452" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q452" t="n">
         <v>0</v>
       </c>
       <c r="R452" t="n">
-        <v>0.1627894735985319</v>
+        <v>0.1647274435223239</v>
       </c>
       <c r="S452" t="inlineStr">
         <is>
@@ -71391,16 +71391,16 @@
         </is>
       </c>
       <c r="N453" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O453" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Q453" t="n">
         <v>0</v>
       </c>
       <c r="R453" t="n">
-        <v>1.145340224961099</v>
+        <v>1.147278194884891</v>
       </c>
       <c r="S453" t="inlineStr">
         <is>
@@ -72575,16 +72575,16 @@
         </is>
       </c>
       <c r="N461" t="n">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="O461" t="n">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="Q461" t="n">
         <v>0</v>
       </c>
       <c r="R461" t="n">
-        <v>4.860428568870451</v>
+        <v>4.858490598946659</v>
       </c>
       <c r="S461" t="inlineStr">
         <is>
@@ -74051,16 +74051,16 @@
         </is>
       </c>
       <c r="N471" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O471" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q471" t="n">
         <v>0</v>
       </c>
       <c r="R471" t="n">
-        <v>0.1647274435223239</v>
+        <v>0.1666654134461159</v>
       </c>
       <c r="S471" t="inlineStr">
         <is>
@@ -77703,16 +77703,16 @@
         </is>
       </c>
       <c r="N495" t="n">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="O495" t="n">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="Q495" t="n">
         <v>0</v>
       </c>
       <c r="R495" t="n">
-        <v>10.76348495674102</v>
+        <v>10.76154698681723</v>
       </c>
       <c r="S495" t="inlineStr">
         <is>
@@ -77865,10 +77865,10 @@
         </is>
       </c>
       <c r="N496" t="n">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="O496" t="n">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="U496" t="inlineStr">
         <is>
@@ -78939,16 +78939,16 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="O502" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Q502" t="n">
         <v>0</v>
       </c>
       <c r="R502" t="n">
-        <v>0.0465112781710091</v>
+        <v>0.06976691725651366</v>
       </c>
       <c r="S502" t="inlineStr">
         <is>
@@ -79087,16 +79087,16 @@
         </is>
       </c>
       <c r="N503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q503" t="n">
         <v>0</v>
       </c>
       <c r="R503" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S503" t="inlineStr">
         <is>
@@ -79235,16 +79235,16 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="O504" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="Q504" t="n">
         <v>0</v>
       </c>
       <c r="R504" t="n">
-        <v>0.1860451126840364</v>
+        <v>0.2151146615409171</v>
       </c>
       <c r="S504" t="inlineStr">
         <is>
@@ -79383,16 +79383,16 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O505" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q505" t="n">
         <v>0</v>
       </c>
       <c r="R505" t="n">
-        <v>0.01356578946654432</v>
+        <v>0.01744172931412841</v>
       </c>
       <c r="S505" t="inlineStr">
         <is>
@@ -80916,16 +80916,16 @@
         </is>
       </c>
       <c r="N514" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O514" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q514" t="n">
         <v>0</v>
       </c>
       <c r="R514" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S514" t="inlineStr">
         <is>
@@ -81212,16 +81212,16 @@
         </is>
       </c>
       <c r="N516" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O516" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q516" t="n">
         <v>0</v>
       </c>
       <c r="R516" t="n">
-        <v>0.02713157893308864</v>
+        <v>0.02906954885688069</v>
       </c>
       <c r="S516" t="inlineStr">
         <is>
@@ -81508,16 +81508,16 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O518" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q518" t="n">
         <v>0</v>
       </c>
       <c r="R518" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.2441842103977978</v>
       </c>
       <c r="S518" t="inlineStr">
         <is>
@@ -81804,16 +81804,16 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="O520" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="Q520" t="n">
         <v>0</v>
       </c>
       <c r="R520" t="n">
-        <v>0.08527067664685002</v>
+        <v>0.09883646611339433</v>
       </c>
       <c r="S520" t="inlineStr">
         <is>
@@ -81966,10 +81966,10 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="O521" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="U521" t="inlineStr">
         <is>
@@ -82348,16 +82348,16 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O523" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q523" t="n">
         <v>0</v>
       </c>
       <c r="R523" t="n">
-        <v>0.02713157893308864</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S523" t="inlineStr">
         <is>
@@ -82496,16 +82496,16 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="O524" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q524" t="n">
         <v>0</v>
       </c>
       <c r="R524" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.2480601502453819</v>
       </c>
       <c r="S524" t="inlineStr">
         <is>
@@ -83680,16 +83680,16 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="O532" t="n">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="Q532" t="n">
         <v>0</v>
       </c>
       <c r="R532" t="n">
-        <v>1.069759397933209</v>
+        <v>1.100766916713882</v>
       </c>
       <c r="S532" t="inlineStr">
         <is>
@@ -85156,16 +85156,16 @@
         </is>
       </c>
       <c r="N542" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O542" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q542" t="n">
         <v>0</v>
       </c>
       <c r="R542" t="n">
-        <v>0.03294548870446478</v>
+        <v>0.04069736839963296</v>
       </c>
       <c r="S542" t="inlineStr">
         <is>
@@ -85748,16 +85748,16 @@
         </is>
       </c>
       <c r="N546" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O546" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q546" t="n">
         <v>0</v>
       </c>
       <c r="R546" t="n">
-        <v>0.01356578946654432</v>
+        <v>0.01744172931412841</v>
       </c>
       <c r="S546" t="inlineStr">
         <is>
@@ -86488,16 +86488,16 @@
         </is>
       </c>
       <c r="N551" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O551" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q551" t="n">
         <v>0</v>
       </c>
       <c r="R551" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S551" t="inlineStr">
         <is>
@@ -88808,16 +88808,16 @@
         </is>
       </c>
       <c r="N566" t="n">
-        <v>1827</v>
+        <v>1976</v>
       </c>
       <c r="O566" t="n">
-        <v>1827</v>
+        <v>1976</v>
       </c>
       <c r="Q566" t="n">
         <v>0</v>
       </c>
       <c r="R566" t="n">
-        <v>3.540671050768068</v>
+        <v>3.829428569413083</v>
       </c>
       <c r="S566" t="inlineStr">
         <is>
@@ -88970,10 +88970,10 @@
         </is>
       </c>
       <c r="N567" t="n">
-        <v>1827</v>
+        <v>1976</v>
       </c>
       <c r="O567" t="n">
-        <v>1827</v>
+        <v>1976</v>
       </c>
       <c r="U567" t="inlineStr">
         <is>
@@ -89711,7 +89711,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>74432</v>
+        <v>74649</v>
       </c>
     </row>
     <row r="16">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -55745,13 +55745,13 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O360" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R360" t="n">
-        <v>0.3837180449108251</v>
+        <v>0.3856560148346171</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
@@ -62431,13 +62431,13 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O404" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R404" t="n">
-        <v>0.2403082705502137</v>
+        <v>0.2422462404740058</v>
       </c>
       <c r="S404" t="inlineStr">
         <is>
@@ -65434,13 +65434,13 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>5089</v>
+        <v>5087</v>
       </c>
       <c r="O424" t="n">
-        <v>5089</v>
+        <v>5087</v>
       </c>
       <c r="R424" t="n">
-        <v>9.862328942177722</v>
+        <v>9.858453002330137</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -65593,10 +65593,10 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>5089</v>
+        <v>5087</v>
       </c>
       <c r="O425" t="n">
-        <v>5089</v>
+        <v>5087</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
@@ -73196,13 +73196,13 @@
         </is>
       </c>
       <c r="N474" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O474" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R474" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.01744172931412841</v>
       </c>
       <c r="S474" t="inlineStr">
         <is>
@@ -73341,13 +73341,13 @@
         </is>
       </c>
       <c r="N475" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O475" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R475" t="n">
-        <v>0.2732537592546785</v>
+        <v>0.2751917291784705</v>
       </c>
       <c r="S475" t="inlineStr">
         <is>
@@ -76344,13 +76344,13 @@
         </is>
       </c>
       <c r="N495" t="n">
-        <v>5552</v>
+        <v>5550</v>
       </c>
       <c r="O495" t="n">
-        <v>5552</v>
+        <v>5550</v>
       </c>
       <c r="R495" t="n">
-        <v>10.75960901689344</v>
+        <v>10.75573307704586</v>
       </c>
       <c r="S495" t="inlineStr">
         <is>
@@ -76503,10 +76503,10 @@
         </is>
       </c>
       <c r="N496" t="n">
-        <v>5552</v>
+        <v>5550</v>
       </c>
       <c r="O496" t="n">
-        <v>5552</v>
+        <v>5550</v>
       </c>
       <c r="U496" t="inlineStr">
         <is>
@@ -77565,13 +77565,13 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="O502" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="R502" t="n">
-        <v>0.06976691725651366</v>
+        <v>0.09689849618960229</v>
       </c>
       <c r="S502" t="inlineStr">
         <is>
@@ -77855,13 +77855,13 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O504" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="R504" t="n">
-        <v>0.2868195487212228</v>
+        <v>0.294571428416391</v>
       </c>
       <c r="S504" t="inlineStr">
         <is>
@@ -78000,13 +78000,13 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O505" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R505" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.02713157893308864</v>
       </c>
       <c r="S505" t="inlineStr">
         <is>
@@ -80092,13 +80092,13 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="O518" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="R518" t="n">
-        <v>0.3003853381877671</v>
+        <v>0.3217030073494796</v>
       </c>
       <c r="S518" t="inlineStr">
         <is>
@@ -80382,13 +80382,13 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="O520" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="R520" t="n">
-        <v>0.1027124059609784</v>
+        <v>0.1220921051988989</v>
       </c>
       <c r="S520" t="inlineStr">
         <is>
@@ -80541,10 +80541,10 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="O521" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="U521" t="inlineStr">
         <is>
@@ -81065,13 +81065,13 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="O524" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="R524" t="n">
-        <v>0.2984473682639751</v>
+        <v>0.3061992479591433</v>
       </c>
       <c r="S524" t="inlineStr">
         <is>
@@ -82225,13 +82225,13 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>669</v>
+        <v>683</v>
       </c>
       <c r="O532" t="n">
-        <v>669</v>
+        <v>683</v>
       </c>
       <c r="R532" t="n">
-        <v>1.296501879016879</v>
+        <v>1.323633457949967</v>
       </c>
       <c r="S532" t="inlineStr">
         <is>
@@ -82515,13 +82515,13 @@
         </is>
       </c>
       <c r="N534" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O534" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R534" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="S534" t="inlineStr">
         <is>
@@ -83526,13 +83526,13 @@
         </is>
       </c>
       <c r="N541" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O541" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R541" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S541" t="inlineStr">
         <is>
@@ -83816,13 +83816,13 @@
         </is>
       </c>
       <c r="N543" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O543" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R543" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S543" t="inlineStr">
         <is>
@@ -84251,13 +84251,13 @@
         </is>
       </c>
       <c r="N546" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O546" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R546" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.02131766916171251</v>
       </c>
       <c r="S546" t="inlineStr">
         <is>
@@ -87254,13 +87254,13 @@
         </is>
       </c>
       <c r="N566" t="n">
-        <v>2159</v>
+        <v>2341</v>
       </c>
       <c r="O566" t="n">
-        <v>2159</v>
+        <v>2341</v>
       </c>
       <c r="R566" t="n">
-        <v>4.184077065467028</v>
+        <v>4.53678759159718</v>
       </c>
       <c r="S566" t="inlineStr">
         <is>
@@ -87413,10 +87413,10 @@
         </is>
       </c>
       <c r="N567" t="n">
-        <v>2159</v>
+        <v>2341</v>
       </c>
       <c r="O567" t="n">
-        <v>2159</v>
+        <v>2341</v>
       </c>
       <c r="U567" t="inlineStr">
         <is>
@@ -88151,7 +88151,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75058</v>
+        <v>75303</v>
       </c>
     </row>
     <row r="16">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -61561,13 +61561,13 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O398" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R398" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S398" t="inlineStr">
         <is>
@@ -61996,13 +61996,13 @@
         </is>
       </c>
       <c r="N401" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O401" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R401" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S401" t="inlineStr">
         <is>
@@ -62431,13 +62431,13 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O404" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="R404" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.2441842103977978</v>
       </c>
       <c r="S404" t="inlineStr">
         <is>
@@ -65434,13 +65434,13 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>5087</v>
+        <v>5082</v>
       </c>
       <c r="O424" t="n">
-        <v>5087</v>
+        <v>5082</v>
       </c>
       <c r="R424" t="n">
-        <v>9.858453002330137</v>
+        <v>9.848763152711177</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -65593,10 +65593,10 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>5087</v>
+        <v>5082</v>
       </c>
       <c r="O425" t="n">
-        <v>5087</v>
+        <v>5082</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
@@ -69182,13 +69182,13 @@
         </is>
       </c>
       <c r="N447" t="n">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="O447" t="n">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="R447" t="n">
-        <v>1.651150375070823</v>
+        <v>1.656964284842199</v>
       </c>
       <c r="S447" t="inlineStr">
         <is>
@@ -70010,13 +70010,13 @@
         </is>
       </c>
       <c r="N452" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O452" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R452" t="n">
-        <v>0.1647274435223239</v>
+        <v>0.1608515036747398</v>
       </c>
       <c r="S452" t="inlineStr">
         <is>
@@ -71315,13 +71315,13 @@
         </is>
       </c>
       <c r="N461" t="n">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="O461" t="n">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="R461" t="n">
-        <v>4.860428568870451</v>
+        <v>4.862366538794243</v>
       </c>
       <c r="S461" t="inlineStr">
         <is>
@@ -72616,13 +72616,13 @@
         </is>
       </c>
       <c r="N470" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O470" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R470" t="n">
-        <v>0.04457330824721705</v>
+        <v>0.04844924809480115</v>
       </c>
       <c r="S470" t="inlineStr">
         <is>
@@ -72761,13 +72761,13 @@
         </is>
       </c>
       <c r="N471" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O471" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R471" t="n">
-        <v>0.1705413532937</v>
+        <v>0.168603383369908</v>
       </c>
       <c r="S471" t="inlineStr">
         <is>
@@ -72906,13 +72906,13 @@
         </is>
       </c>
       <c r="N472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R472" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S472" t="inlineStr">
         <is>
@@ -76344,13 +76344,13 @@
         </is>
       </c>
       <c r="N495" t="n">
-        <v>5550</v>
+        <v>5544</v>
       </c>
       <c r="O495" t="n">
-        <v>5550</v>
+        <v>5544</v>
       </c>
       <c r="R495" t="n">
-        <v>10.75573307704586</v>
+        <v>10.7441052575031</v>
       </c>
       <c r="S495" t="inlineStr">
         <is>
@@ -76503,10 +76503,10 @@
         </is>
       </c>
       <c r="N496" t="n">
-        <v>5550</v>
+        <v>5544</v>
       </c>
       <c r="O496" t="n">
-        <v>5550</v>
+        <v>5544</v>
       </c>
       <c r="U496" t="inlineStr">
         <is>
@@ -77565,13 +77565,13 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="O502" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="R502" t="n">
-        <v>0.09689849618960229</v>
+        <v>0.1085263157323546</v>
       </c>
       <c r="S502" t="inlineStr">
         <is>
@@ -77855,13 +77855,13 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="O504" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="R504" t="n">
-        <v>0.294571428416391</v>
+        <v>0.3720902253680728</v>
       </c>
       <c r="S504" t="inlineStr">
         <is>
@@ -78000,13 +78000,13 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O505" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R505" t="n">
-        <v>0.02713157893308864</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S505" t="inlineStr">
         <is>
@@ -79077,13 +79077,13 @@
         </is>
       </c>
       <c r="N511" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O511" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R511" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S511" t="inlineStr">
         <is>
@@ -79512,13 +79512,13 @@
         </is>
       </c>
       <c r="N514" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O514" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R514" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S514" t="inlineStr">
         <is>
@@ -79802,13 +79802,13 @@
         </is>
       </c>
       <c r="N516" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O516" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R516" t="n">
-        <v>0.02906954885688069</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="S516" t="inlineStr">
         <is>
@@ -80092,13 +80092,13 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="O518" t="n">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="R518" t="n">
-        <v>0.3217030073494796</v>
+        <v>0.4767406012528433</v>
       </c>
       <c r="S518" t="inlineStr">
         <is>
@@ -80382,13 +80382,13 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="O520" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="R520" t="n">
-        <v>0.1220921051988989</v>
+        <v>0.1453477442844034</v>
       </c>
       <c r="S520" t="inlineStr">
         <is>
@@ -80541,10 +80541,10 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="O521" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="U521" t="inlineStr">
         <is>
@@ -80920,13 +80920,13 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O523" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R523" t="n">
-        <v>0.03488345862825683</v>
+        <v>0.04457330824721705</v>
       </c>
       <c r="S523" t="inlineStr">
         <is>
@@ -81065,13 +81065,13 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="O524" t="n">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="R524" t="n">
-        <v>0.3061992479591433</v>
+        <v>0.3953458644535773</v>
       </c>
       <c r="S524" t="inlineStr">
         <is>
@@ -81935,13 +81935,13 @@
         </is>
       </c>
       <c r="N530" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O530" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R530" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S530" t="inlineStr">
         <is>
@@ -82225,13 +82225,13 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>683</v>
+        <v>828</v>
       </c>
       <c r="O532" t="n">
-        <v>683</v>
+        <v>828</v>
       </c>
       <c r="R532" t="n">
-        <v>1.323633457949967</v>
+        <v>1.604639096899814</v>
       </c>
       <c r="S532" t="inlineStr">
         <is>
@@ -82370,13 +82370,13 @@
         </is>
       </c>
       <c r="N533" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O533" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R533" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S533" t="inlineStr">
         <is>
@@ -83526,13 +83526,13 @@
         </is>
       </c>
       <c r="N541" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O541" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R541" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.02325563908550455</v>
       </c>
       <c r="S541" t="inlineStr">
         <is>
@@ -83671,13 +83671,13 @@
         </is>
       </c>
       <c r="N542" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="O542" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="R542" t="n">
-        <v>0.04069736839963296</v>
+        <v>0.06589097740892956</v>
       </c>
       <c r="S542" t="inlineStr">
         <is>
@@ -84251,13 +84251,13 @@
         </is>
       </c>
       <c r="N546" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O546" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R546" t="n">
-        <v>0.02131766916171251</v>
+        <v>0.02906954885688069</v>
       </c>
       <c r="S546" t="inlineStr">
         <is>
@@ -87254,13 +87254,13 @@
         </is>
       </c>
       <c r="N566" t="n">
-        <v>2341</v>
+        <v>2729</v>
       </c>
       <c r="O566" t="n">
-        <v>2341</v>
+        <v>2729</v>
       </c>
       <c r="R566" t="n">
-        <v>4.53678759159718</v>
+        <v>5.288719922028493</v>
       </c>
       <c r="S566" t="inlineStr">
         <is>
@@ -87413,10 +87413,10 @@
         </is>
       </c>
       <c r="N567" t="n">
-        <v>2341</v>
+        <v>2729</v>
       </c>
       <c r="O567" t="n">
-        <v>2341</v>
+        <v>2729</v>
       </c>
       <c r="U567" t="inlineStr">
         <is>
@@ -88151,7 +88151,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75303</v>
+        <v>76048</v>
       </c>
     </row>
     <row r="16">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -56035,13 +56035,13 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="O362" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="R362" t="n">
-        <v>0.844954886773332</v>
+        <v>0.841078946925748</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
@@ -58272,13 +58272,13 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="O376" t="n">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="R376" t="n">
-        <v>2.329439848398039</v>
+        <v>2.325563908550455</v>
       </c>
       <c r="S376" t="inlineStr">
         <is>
@@ -60405,13 +60405,13 @@
         </is>
       </c>
       <c r="N390" t="n">
-        <v>3557</v>
+        <v>3561</v>
       </c>
       <c r="O390" t="n">
-        <v>3557</v>
+        <v>3561</v>
       </c>
       <c r="R390" t="n">
-        <v>6.893359018928308</v>
+        <v>6.901110898623476</v>
       </c>
       <c r="S390" t="inlineStr">
         <is>
@@ -61851,13 +61851,13 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O400" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R400" t="n">
-        <v>0.1104642856561466</v>
+        <v>0.1143402255037307</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
@@ -62431,13 +62431,13 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O404" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R404" t="n">
-        <v>0.2441842103977978</v>
+        <v>0.2422462404740058</v>
       </c>
       <c r="S404" t="inlineStr">
         <is>
@@ -65434,13 +65434,13 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>5082</v>
+        <v>5078</v>
       </c>
       <c r="O424" t="n">
-        <v>5082</v>
+        <v>5078</v>
       </c>
       <c r="R424" t="n">
-        <v>9.848763152711177</v>
+        <v>9.841011273016008</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -65593,10 +65593,10 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>5082</v>
+        <v>5078</v>
       </c>
       <c r="O425" t="n">
-        <v>5082</v>
+        <v>5078</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
@@ -66945,13 +66945,13 @@
         </is>
       </c>
       <c r="N433" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O433" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="R433" t="n">
-        <v>0.8643345860112523</v>
+        <v>0.8662725559350446</v>
       </c>
       <c r="S433" t="inlineStr">
         <is>
@@ -69182,13 +69182,13 @@
         </is>
       </c>
       <c r="N447" t="n">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O447" t="n">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="R447" t="n">
-        <v>1.656964284842199</v>
+        <v>1.655026314918407</v>
       </c>
       <c r="S447" t="inlineStr">
         <is>
@@ -70445,13 +70445,13 @@
         </is>
       </c>
       <c r="N455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R455" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S455" t="inlineStr">
         <is>
@@ -71315,13 +71315,13 @@
         </is>
       </c>
       <c r="N461" t="n">
-        <v>2509</v>
+        <v>2512</v>
       </c>
       <c r="O461" t="n">
-        <v>2509</v>
+        <v>2512</v>
       </c>
       <c r="R461" t="n">
-        <v>4.862366538794243</v>
+        <v>4.86818044856562</v>
       </c>
       <c r="S461" t="inlineStr">
         <is>
@@ -71605,13 +71605,13 @@
         </is>
       </c>
       <c r="N463" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O463" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R463" t="n">
-        <v>0.03488345862825683</v>
+        <v>0.03682142855204888</v>
       </c>
       <c r="S463" t="inlineStr">
         <is>
@@ -72761,13 +72761,13 @@
         </is>
       </c>
       <c r="N471" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="O471" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="R471" t="n">
-        <v>0.168603383369908</v>
+        <v>0.1821691728364523</v>
       </c>
       <c r="S471" t="inlineStr">
         <is>
@@ -73196,13 +73196,13 @@
         </is>
       </c>
       <c r="N474" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O474" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R474" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S474" t="inlineStr">
         <is>
@@ -73341,13 +73341,13 @@
         </is>
       </c>
       <c r="N475" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O475" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="R475" t="n">
-        <v>0.2751917291784705</v>
+        <v>0.2790676690260546</v>
       </c>
       <c r="S475" t="inlineStr">
         <is>
@@ -76344,13 +76344,13 @@
         </is>
       </c>
       <c r="N495" t="n">
-        <v>5544</v>
+        <v>5538</v>
       </c>
       <c r="O495" t="n">
-        <v>5544</v>
+        <v>5538</v>
       </c>
       <c r="R495" t="n">
-        <v>10.7441052575031</v>
+        <v>10.73247743796035</v>
       </c>
       <c r="S495" t="inlineStr">
         <is>
@@ -76503,10 +76503,10 @@
         </is>
       </c>
       <c r="N496" t="n">
-        <v>5544</v>
+        <v>5538</v>
       </c>
       <c r="O496" t="n">
-        <v>5544</v>
+        <v>5538</v>
       </c>
       <c r="U496" t="inlineStr">
         <is>
@@ -76737,13 +76737,13 @@
         </is>
       </c>
       <c r="N497" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O497" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R497" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S497" t="inlineStr">
         <is>
@@ -76896,10 +76896,10 @@
         </is>
       </c>
       <c r="N498" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O498" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U498" t="inlineStr">
         <is>
@@ -77565,13 +77565,13 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="O502" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="R502" t="n">
-        <v>0.1085263157323546</v>
+        <v>0.1821691728364523</v>
       </c>
       <c r="S502" t="inlineStr">
         <is>
@@ -77710,13 +77710,13 @@
         </is>
       </c>
       <c r="N503" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O503" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R503" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S503" t="inlineStr">
         <is>
@@ -77855,13 +77855,13 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>192</v>
+        <v>308</v>
       </c>
       <c r="O504" t="n">
-        <v>192</v>
+        <v>308</v>
       </c>
       <c r="R504" t="n">
-        <v>0.3720902253680728</v>
+        <v>0.5968947365279502</v>
       </c>
       <c r="S504" t="inlineStr">
         <is>
@@ -78000,13 +78000,13 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O505" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="R505" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.0465112781710091</v>
       </c>
       <c r="S505" t="inlineStr">
         <is>
@@ -79077,13 +79077,13 @@
         </is>
       </c>
       <c r="N511" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O511" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R511" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="S511" t="inlineStr">
         <is>
@@ -79512,13 +79512,13 @@
         </is>
       </c>
       <c r="N514" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O514" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R514" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.02906954885688069</v>
       </c>
       <c r="S514" t="inlineStr">
         <is>
@@ -79802,13 +79802,13 @@
         </is>
       </c>
       <c r="N516" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="O516" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="R516" t="n">
-        <v>0.03294548870446478</v>
+        <v>0.05813909771376138</v>
       </c>
       <c r="S516" t="inlineStr">
         <is>
@@ -80092,13 +80092,13 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>246</v>
+        <v>371</v>
       </c>
       <c r="O518" t="n">
-        <v>246</v>
+        <v>371</v>
       </c>
       <c r="R518" t="n">
-        <v>0.4767406012528433</v>
+        <v>0.718986841726849</v>
       </c>
       <c r="S518" t="inlineStr">
         <is>
@@ -80237,13 +80237,13 @@
         </is>
       </c>
       <c r="N519" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O519" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R519" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S519" t="inlineStr">
         <is>
@@ -80382,13 +80382,13 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="O520" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="R520" t="n">
-        <v>0.1453477442844034</v>
+        <v>0.2422462404740058</v>
       </c>
       <c r="S520" t="inlineStr">
         <is>
@@ -80541,10 +80541,10 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="O521" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="U521" t="inlineStr">
         <is>
@@ -80775,13 +80775,13 @@
         </is>
       </c>
       <c r="N522" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O522" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R522" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S522" t="inlineStr">
         <is>
@@ -80920,13 +80920,13 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="O523" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R523" t="n">
-        <v>0.04457330824721705</v>
+        <v>0.0717048871803057</v>
       </c>
       <c r="S523" t="inlineStr">
         <is>
@@ -81065,13 +81065,13 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>204</v>
+        <v>320</v>
       </c>
       <c r="O524" t="n">
-        <v>204</v>
+        <v>320</v>
       </c>
       <c r="R524" t="n">
-        <v>0.3953458644535773</v>
+        <v>0.6201503756134548</v>
       </c>
       <c r="S524" t="inlineStr">
         <is>
@@ -81790,13 +81790,13 @@
         </is>
       </c>
       <c r="N529" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O529" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R529" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S529" t="inlineStr">
         <is>
@@ -82225,13 +82225,13 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>828</v>
+        <v>1308</v>
       </c>
       <c r="O532" t="n">
-        <v>828</v>
+        <v>1308</v>
       </c>
       <c r="R532" t="n">
-        <v>1.604639096899814</v>
+        <v>2.534864660319996</v>
       </c>
       <c r="S532" t="inlineStr">
         <is>
@@ -82370,13 +82370,13 @@
         </is>
       </c>
       <c r="N533" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O533" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R533" t="n">
-        <v>0.01356578946654432</v>
+        <v>0.02325563908550455</v>
       </c>
       <c r="S533" t="inlineStr">
         <is>
@@ -82515,13 +82515,13 @@
         </is>
       </c>
       <c r="N534" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O534" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R534" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S534" t="inlineStr">
         <is>
@@ -83381,13 +83381,13 @@
         </is>
       </c>
       <c r="N540" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O540" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R540" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S540" t="inlineStr">
         <is>
@@ -83526,13 +83526,13 @@
         </is>
       </c>
       <c r="N541" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O541" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R541" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S541" t="inlineStr">
         <is>
@@ -83671,13 +83671,13 @@
         </is>
       </c>
       <c r="N542" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O542" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R542" t="n">
-        <v>0.06589097740892956</v>
+        <v>0.08720864657064206</v>
       </c>
       <c r="S542" t="inlineStr">
         <is>
@@ -83816,13 +83816,13 @@
         </is>
       </c>
       <c r="N543" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O543" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R543" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S543" t="inlineStr">
         <is>
@@ -84106,13 +84106,13 @@
         </is>
       </c>
       <c r="N545" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O545" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R545" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S545" t="inlineStr">
         <is>
@@ -84251,13 +84251,13 @@
         </is>
       </c>
       <c r="N546" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O546" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="R546" t="n">
-        <v>0.02906954885688069</v>
+        <v>0.06007706763755342</v>
       </c>
       <c r="S546" t="inlineStr">
         <is>
@@ -84976,13 +84976,13 @@
         </is>
       </c>
       <c r="N551" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O551" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R551" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S551" t="inlineStr">
         <is>
@@ -87254,13 +87254,13 @@
         </is>
       </c>
       <c r="N566" t="n">
-        <v>2729</v>
+        <v>4426</v>
       </c>
       <c r="O566" t="n">
-        <v>2729</v>
+        <v>4426</v>
       </c>
       <c r="R566" t="n">
-        <v>5.288719922028493</v>
+        <v>8.577454882703595</v>
       </c>
       <c r="S566" t="inlineStr">
         <is>
@@ -87413,10 +87413,10 @@
         </is>
       </c>
       <c r="N567" t="n">
-        <v>2729</v>
+        <v>4426</v>
       </c>
       <c r="O567" t="n">
-        <v>2729</v>
+        <v>4426</v>
       </c>
       <c r="U567" t="inlineStr">
         <is>
@@ -88151,7 +88151,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>76048</v>
+        <v>78771</v>
       </c>
     </row>
     <row r="16">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -56035,13 +56035,13 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O362" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="R362" t="n">
-        <v>0.841078946925748</v>
+        <v>0.844954886773332</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
@@ -56180,13 +56180,13 @@
         </is>
       </c>
       <c r="N363" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O363" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R363" t="n">
-        <v>0.1472857142081955</v>
+        <v>0.1453477442844034</v>
       </c>
       <c r="S363" t="inlineStr">
         <is>
@@ -58272,13 +58272,13 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="O376" t="n">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="R376" t="n">
-        <v>2.325563908550455</v>
+        <v>2.329439848398039</v>
       </c>
       <c r="S376" t="inlineStr">
         <is>
@@ -69182,13 +69182,13 @@
         </is>
       </c>
       <c r="N447" t="n">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="O447" t="n">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="R447" t="n">
-        <v>1.655026314918407</v>
+        <v>1.651150375070823</v>
       </c>
       <c r="S447" t="inlineStr">
         <is>
@@ -70445,13 +70445,13 @@
         </is>
       </c>
       <c r="N455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R455" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S455" t="inlineStr">
         <is>
@@ -72761,13 +72761,13 @@
         </is>
       </c>
       <c r="N471" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O471" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="R471" t="n">
-        <v>0.1821691728364523</v>
+        <v>0.1782932329888682</v>
       </c>
       <c r="S471" t="inlineStr">
         <is>
@@ -73341,13 +73341,13 @@
         </is>
       </c>
       <c r="N475" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O475" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="R475" t="n">
-        <v>0.2790676690260546</v>
+        <v>0.2810056389498466</v>
       </c>
       <c r="S475" t="inlineStr">
         <is>
@@ -77565,13 +77565,13 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="O502" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="R502" t="n">
-        <v>0.1821691728364523</v>
+        <v>0.1918590224554125</v>
       </c>
       <c r="S502" t="inlineStr">
         <is>
@@ -77855,13 +77855,13 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="O504" t="n">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="R504" t="n">
-        <v>0.5968947365279502</v>
+        <v>0.6104605259944944</v>
       </c>
       <c r="S504" t="inlineStr">
         <is>
@@ -78000,13 +78000,13 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O505" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R505" t="n">
-        <v>0.0465112781710091</v>
+        <v>0.04844924809480115</v>
       </c>
       <c r="S505" t="inlineStr">
         <is>
@@ -79802,13 +79802,13 @@
         </is>
       </c>
       <c r="N516" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O516" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R516" t="n">
-        <v>0.05813909771376138</v>
+        <v>0.06395300748513752</v>
       </c>
       <c r="S516" t="inlineStr">
         <is>
@@ -80092,13 +80092,13 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="O518" t="n">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="R518" t="n">
-        <v>0.718986841726849</v>
+        <v>0.7713120296692343</v>
       </c>
       <c r="S518" t="inlineStr">
         <is>
@@ -80382,13 +80382,13 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="O520" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="R520" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.2558120299405501</v>
       </c>
       <c r="S520" t="inlineStr">
         <is>
@@ -80541,10 +80541,10 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="O521" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="U521" t="inlineStr">
         <is>
@@ -80920,13 +80920,13 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O523" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R523" t="n">
-        <v>0.0717048871803057</v>
+        <v>0.07364285710409775</v>
       </c>
       <c r="S523" t="inlineStr">
         <is>
@@ -81065,13 +81065,13 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O524" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="R524" t="n">
-        <v>0.6201503756134548</v>
+        <v>0.6240263154610388</v>
       </c>
       <c r="S524" t="inlineStr">
         <is>
@@ -82225,13 +82225,13 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>1308</v>
+        <v>1317</v>
       </c>
       <c r="O532" t="n">
-        <v>1308</v>
+        <v>1317</v>
       </c>
       <c r="R532" t="n">
-        <v>2.534864660319996</v>
+        <v>2.552306389634124</v>
       </c>
       <c r="S532" t="inlineStr">
         <is>
@@ -82370,13 +82370,13 @@
         </is>
       </c>
       <c r="N533" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O533" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R533" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.02713157893308864</v>
       </c>
       <c r="S533" t="inlineStr">
         <is>
@@ -83526,13 +83526,13 @@
         </is>
       </c>
       <c r="N541" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O541" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R541" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="S541" t="inlineStr">
         <is>
@@ -83671,13 +83671,13 @@
         </is>
       </c>
       <c r="N542" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O542" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R542" t="n">
-        <v>0.08720864657064206</v>
+        <v>0.09108458641822616</v>
       </c>
       <c r="S542" t="inlineStr">
         <is>
@@ -84106,13 +84106,13 @@
         </is>
       </c>
       <c r="N545" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O545" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R545" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S545" t="inlineStr">
         <is>
@@ -87254,13 +87254,13 @@
         </is>
       </c>
       <c r="N566" t="n">
-        <v>4426</v>
+        <v>4440</v>
       </c>
       <c r="O566" t="n">
-        <v>4426</v>
+        <v>4440</v>
       </c>
       <c r="R566" t="n">
-        <v>8.577454882703595</v>
+        <v>8.604586461636684</v>
       </c>
       <c r="S566" t="inlineStr">
         <is>
@@ -87413,10 +87413,10 @@
         </is>
       </c>
       <c r="N567" t="n">
-        <v>4426</v>
+        <v>4440</v>
       </c>
       <c r="O567" t="n">
-        <v>4426</v>
+        <v>4440</v>
       </c>
       <c r="U567" t="inlineStr">
         <is>
@@ -88151,7 +88151,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>78771</v>
+        <v>78854</v>
       </c>
     </row>
     <row r="16">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -13315,7 +13315,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26073,7 +26073,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -32945,7 +32945,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -35135,7 +35135,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -36983,7 +36983,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -42882,7 +42882,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -43855,7 +43855,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -45806,7 +45806,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -46045,7 +46045,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -47893,7 +47893,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -53792,7 +53792,7 @@
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
@@ -54765,7 +54765,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -56716,7 +56716,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -56955,7 +56955,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -58803,7 +58803,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -64702,7 +64702,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -65675,7 +65675,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -67626,7 +67626,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -67865,7 +67865,7 @@
       </c>
       <c r="AJ438" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK438" t="inlineStr">
@@ -69713,7 +69713,7 @@
       </c>
       <c r="AJ450" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK450" t="inlineStr">
@@ -75612,7 +75612,7 @@
       </c>
       <c r="AJ490" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK490" t="inlineStr">
@@ -76585,7 +76585,7 @@
       </c>
       <c r="AJ496" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK496" t="inlineStr">
@@ -78536,7 +78536,7 @@
       </c>
       <c r="AJ508" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK508" t="inlineStr">
@@ -78775,7 +78775,7 @@
       </c>
       <c r="AJ509" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK509" t="inlineStr">
@@ -80623,7 +80623,7 @@
       </c>
       <c r="AJ521" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK521" t="inlineStr">
@@ -86522,7 +86522,7 @@
       </c>
       <c r="AJ561" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK561" t="inlineStr">
@@ -87495,7 +87495,7 @@
       </c>
       <c r="AJ567" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK567" t="inlineStr">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -13315,7 +13315,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26073,7 +26073,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -32945,7 +32945,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -35135,7 +35135,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -36983,7 +36983,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -42882,7 +42882,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -43855,7 +43855,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -45806,7 +45806,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -46045,7 +46045,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -47893,7 +47893,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -53792,7 +53792,7 @@
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
@@ -54765,7 +54765,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -56716,7 +56716,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -56955,7 +56955,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -58803,7 +58803,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -64702,7 +64702,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -65675,7 +65675,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -67626,7 +67626,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -67865,7 +67865,7 @@
       </c>
       <c r="AJ438" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK438" t="inlineStr">
@@ -69713,7 +69713,7 @@
       </c>
       <c r="AJ450" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK450" t="inlineStr">
@@ -75612,7 +75612,7 @@
       </c>
       <c r="AJ490" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK490" t="inlineStr">
@@ -76585,7 +76585,7 @@
       </c>
       <c r="AJ496" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK496" t="inlineStr">
@@ -78536,7 +78536,7 @@
       </c>
       <c r="AJ508" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK508" t="inlineStr">
@@ -78775,7 +78775,7 @@
       </c>
       <c r="AJ509" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK509" t="inlineStr">
@@ -80623,7 +80623,7 @@
       </c>
       <c r="AJ521" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK521" t="inlineStr">
@@ -86522,7 +86522,7 @@
       </c>
       <c r="AJ561" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK561" t="inlineStr">
@@ -87495,7 +87495,7 @@
       </c>
       <c r="AJ567" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK567" t="inlineStr">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -13315,7 +13315,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26073,7 +26073,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -32945,7 +32945,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -35135,7 +35135,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -36983,7 +36983,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -42882,7 +42882,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -43855,7 +43855,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -45806,7 +45806,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -46045,7 +46045,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -47893,7 +47893,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -53792,7 +53792,7 @@
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
@@ -54765,7 +54765,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -56716,7 +56716,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -56955,7 +56955,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -58803,7 +58803,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -64702,7 +64702,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -65675,7 +65675,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -67626,7 +67626,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -67865,7 +67865,7 @@
       </c>
       <c r="AJ438" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK438" t="inlineStr">
@@ -69713,7 +69713,7 @@
       </c>
       <c r="AJ450" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK450" t="inlineStr">
@@ -75612,7 +75612,7 @@
       </c>
       <c r="AJ490" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK490" t="inlineStr">
@@ -76585,7 +76585,7 @@
       </c>
       <c r="AJ496" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK496" t="inlineStr">
@@ -78536,7 +78536,7 @@
       </c>
       <c r="AJ508" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK508" t="inlineStr">
@@ -78775,7 +78775,7 @@
       </c>
       <c r="AJ509" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK509" t="inlineStr">
@@ -80623,7 +80623,7 @@
       </c>
       <c r="AJ521" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK521" t="inlineStr">
@@ -86522,7 +86522,7 @@
       </c>
       <c r="AJ561" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK561" t="inlineStr">
@@ -87495,7 +87495,7 @@
       </c>
       <c r="AJ567" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK567" t="inlineStr">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -58272,13 +58272,13 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="O376" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="R376" t="n">
-        <v>2.329439848398039</v>
+        <v>2.333315788245623</v>
       </c>
       <c r="S376" t="inlineStr">
         <is>
@@ -62431,13 +62431,13 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O404" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R404" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.2403082705502137</v>
       </c>
       <c r="S404" t="inlineStr">
         <is>
@@ -71315,13 +71315,13 @@
         </is>
       </c>
       <c r="N461" t="n">
-        <v>2512</v>
+        <v>2516</v>
       </c>
       <c r="O461" t="n">
-        <v>2512</v>
+        <v>2516</v>
       </c>
       <c r="R461" t="n">
-        <v>4.86818044856562</v>
+        <v>4.875932328260788</v>
       </c>
       <c r="S461" t="inlineStr">
         <is>
@@ -72761,13 +72761,13 @@
         </is>
       </c>
       <c r="N471" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O471" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R471" t="n">
-        <v>0.1782932329888682</v>
+        <v>0.1802312029126603</v>
       </c>
       <c r="S471" t="inlineStr">
         <is>
@@ -73341,13 +73341,13 @@
         </is>
       </c>
       <c r="N475" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O475" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="R475" t="n">
-        <v>0.2810056389498466</v>
+        <v>0.2829436088736387</v>
       </c>
       <c r="S475" t="inlineStr">
         <is>
@@ -74066,13 +74066,13 @@
         </is>
       </c>
       <c r="N480" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O480" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R480" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S480" t="inlineStr">
         <is>
@@ -76344,13 +76344,13 @@
         </is>
       </c>
       <c r="N495" t="n">
-        <v>5538</v>
+        <v>5536</v>
       </c>
       <c r="O495" t="n">
-        <v>5538</v>
+        <v>5536</v>
       </c>
       <c r="R495" t="n">
-        <v>10.73247743796035</v>
+        <v>10.72860149811277</v>
       </c>
       <c r="S495" t="inlineStr">
         <is>
@@ -76503,10 +76503,10 @@
         </is>
       </c>
       <c r="N496" t="n">
-        <v>5538</v>
+        <v>5536</v>
       </c>
       <c r="O496" t="n">
-        <v>5538</v>
+        <v>5536</v>
       </c>
       <c r="U496" t="inlineStr">
         <is>
@@ -77565,13 +77565,13 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="O502" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="R502" t="n">
-        <v>0.1918590224554125</v>
+        <v>0.2054248119219569</v>
       </c>
       <c r="S502" t="inlineStr">
         <is>
@@ -77710,13 +77710,13 @@
         </is>
       </c>
       <c r="N503" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O503" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R503" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01744172931412841</v>
       </c>
       <c r="S503" t="inlineStr">
         <is>
@@ -77855,13 +77855,13 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>315</v>
+        <v>368</v>
       </c>
       <c r="O504" t="n">
-        <v>315</v>
+        <v>368</v>
       </c>
       <c r="R504" t="n">
-        <v>0.6104605259944944</v>
+        <v>0.7131729319554728</v>
       </c>
       <c r="S504" t="inlineStr">
         <is>
@@ -78000,13 +78000,13 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O505" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R505" t="n">
-        <v>0.04844924809480115</v>
+        <v>0.05426315786617728</v>
       </c>
       <c r="S505" t="inlineStr">
         <is>
@@ -79512,13 +79512,13 @@
         </is>
       </c>
       <c r="N514" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O514" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R514" t="n">
-        <v>0.02906954885688069</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S514" t="inlineStr">
         <is>
@@ -79802,13 +79802,13 @@
         </is>
       </c>
       <c r="N516" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="O516" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="R516" t="n">
-        <v>0.06395300748513752</v>
+        <v>0.07751879695168185</v>
       </c>
       <c r="S516" t="inlineStr">
         <is>
@@ -80092,13 +80092,13 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>398</v>
+        <v>432</v>
       </c>
       <c r="O518" t="n">
-        <v>398</v>
+        <v>432</v>
       </c>
       <c r="R518" t="n">
-        <v>0.7713120296692343</v>
+        <v>0.8372030070781639</v>
       </c>
       <c r="S518" t="inlineStr">
         <is>
@@ -80382,13 +80382,13 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="O520" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="R520" t="n">
-        <v>0.2558120299405501</v>
+        <v>0.2771296991022626</v>
       </c>
       <c r="S520" t="inlineStr">
         <is>
@@ -80541,10 +80541,10 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="O521" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="U521" t="inlineStr">
         <is>
@@ -80920,13 +80920,13 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O523" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R523" t="n">
-        <v>0.07364285710409775</v>
+        <v>0.07558082702788979</v>
       </c>
       <c r="S523" t="inlineStr">
         <is>
@@ -81065,13 +81065,13 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="O524" t="n">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="R524" t="n">
-        <v>0.6240263154610388</v>
+        <v>0.6530958643179194</v>
       </c>
       <c r="S524" t="inlineStr">
         <is>
@@ -81355,13 +81355,13 @@
         </is>
       </c>
       <c r="N526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R526" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S526" t="inlineStr">
         <is>
@@ -82225,13 +82225,13 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>1317</v>
+        <v>1353</v>
       </c>
       <c r="O532" t="n">
-        <v>1317</v>
+        <v>1353</v>
       </c>
       <c r="R532" t="n">
-        <v>2.552306389634124</v>
+        <v>2.622073306890638</v>
       </c>
       <c r="S532" t="inlineStr">
         <is>
@@ -82370,13 +82370,13 @@
         </is>
       </c>
       <c r="N533" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O533" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R533" t="n">
-        <v>0.02713157893308864</v>
+        <v>0.02906954885688069</v>
       </c>
       <c r="S533" t="inlineStr">
         <is>
@@ -82515,13 +82515,13 @@
         </is>
       </c>
       <c r="N534" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O534" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R534" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="S534" t="inlineStr">
         <is>
@@ -83526,13 +83526,13 @@
         </is>
       </c>
       <c r="N541" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O541" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R541" t="n">
-        <v>0.03294548870446478</v>
+        <v>0.03875939847584092</v>
       </c>
       <c r="S541" t="inlineStr">
         <is>
@@ -83671,13 +83671,13 @@
         </is>
       </c>
       <c r="N542" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O542" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="R542" t="n">
-        <v>0.09108458641822616</v>
+        <v>0.09883646611339433</v>
       </c>
       <c r="S542" t="inlineStr">
         <is>
@@ -84251,13 +84251,13 @@
         </is>
       </c>
       <c r="N546" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="O546" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="R546" t="n">
-        <v>0.06007706763755342</v>
+        <v>0.06976691725651366</v>
       </c>
       <c r="S546" t="inlineStr">
         <is>
@@ -84831,13 +84831,13 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O550" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R550" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S550" t="inlineStr">
         <is>
@@ -84976,13 +84976,13 @@
         </is>
       </c>
       <c r="N551" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O551" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R551" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S551" t="inlineStr">
         <is>
@@ -87254,13 +87254,13 @@
         </is>
       </c>
       <c r="N566" t="n">
-        <v>4440</v>
+        <v>4554</v>
       </c>
       <c r="O566" t="n">
-        <v>4440</v>
+        <v>4554</v>
       </c>
       <c r="R566" t="n">
-        <v>8.604586461636684</v>
+        <v>8.825515032948976</v>
       </c>
       <c r="S566" t="inlineStr">
         <is>
@@ -87413,10 +87413,10 @@
         </is>
       </c>
       <c r="N567" t="n">
-        <v>4440</v>
+        <v>4554</v>
       </c>
       <c r="O567" t="n">
-        <v>4440</v>
+        <v>4554</v>
       </c>
       <c r="U567" t="inlineStr">
         <is>
@@ -88151,7 +88151,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>78854</v>
+        <v>79168</v>
       </c>
     </row>
     <row r="16">

--- a/countries/kr/2026-2029.xlsx
+++ b/countries/kr/2026-2029.xlsx
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -13315,7 +13315,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26073,7 +26073,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -32945,7 +32945,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -35135,7 +35135,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -36983,7 +36983,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -42882,7 +42882,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -43855,7 +43855,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -45806,7 +45806,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -46045,7 +46045,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -47893,7 +47893,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -53792,7 +53792,7 @@
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
@@ -54765,7 +54765,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -56716,7 +56716,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -56955,7 +56955,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -58803,7 +58803,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -64702,7 +64702,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -65675,7 +65675,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -67626,7 +67626,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -67865,7 +67865,7 @@
       </c>
       <c r="AJ438" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK438" t="inlineStr">
@@ -69713,7 +69713,7 @@
       </c>
       <c r="AJ450" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK450" t="inlineStr">
@@ -75612,7 +75612,7 @@
       </c>
       <c r="AJ490" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK490" t="inlineStr">
@@ -76585,7 +76585,7 @@
       </c>
       <c r="AJ496" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK496" t="inlineStr">
@@ -78536,7 +78536,7 @@
       </c>
       <c r="AJ508" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK508" t="inlineStr">
@@ -78775,7 +78775,7 @@
       </c>
       <c r="AJ509" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK509" t="inlineStr">
@@ -80623,7 +80623,7 @@
       </c>
       <c r="AJ521" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK521" t="inlineStr">
@@ -86522,7 +86522,7 @@
       </c>
       <c r="AJ561" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK561" t="inlineStr">
@@ -87495,7 +87495,7 @@
       </c>
       <c r="AJ567" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK567" t="inlineStr">
